--- a/6_semestar/Poeni.xlsx
+++ b/6_semestar/Poeni.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ndzn\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\Fakultetski_Materijal\6_semestar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76622113-B801-4FE7-A92F-60BBAF3C5C66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46FC1905-8F4E-4823-9DB7-5836E0534A4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -385,25 +385,25 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -767,7 +767,7 @@
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
       <c r="M9" s="6">
-        <v>15.44</v>
+        <v>20</v>
       </c>
       <c r="N9" s="5"/>
       <c r="O9" s="6"/>
@@ -776,10 +776,10 @@
       <c r="R9" s="5"/>
       <c r="S9" s="5"/>
       <c r="T9" s="6">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="U9" s="6">
-        <v>7.75</v>
+        <v>17.75</v>
       </c>
       <c r="V9" s="7"/>
     </row>
@@ -849,7 +849,9 @@
         <v>17</v>
       </c>
       <c r="K13" s="5"/>
-      <c r="L13" s="6"/>
+      <c r="L13" s="6">
+        <v>4.5</v>
+      </c>
       <c r="M13" s="6"/>
       <c r="N13" s="5"/>
       <c r="O13" s="5"/>
@@ -928,7 +930,7 @@
       <c r="R17" s="5"/>
       <c r="S17" s="5"/>
       <c r="T17" s="6">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="U17" s="8"/>
       <c r="V17" s="7"/>
@@ -943,11 +945,11 @@
       </c>
       <c r="L18" s="13">
         <f t="shared" ref="L18:V18" si="0">SUM(L9:L17)</f>
-        <v>24.5</v>
+        <v>29</v>
       </c>
       <c r="M18" s="13">
         <f t="shared" si="0"/>
-        <v>50.94</v>
+        <v>55.5</v>
       </c>
       <c r="N18" s="13">
         <f t="shared" si="0"/>
@@ -975,11 +977,11 @@
       </c>
       <c r="T18" s="13">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="U18" s="13">
         <f t="shared" si="0"/>
-        <v>7.75</v>
+        <v>17.75</v>
       </c>
       <c r="V18" s="14">
         <f t="shared" si="0"/>

--- a/6_semestar/Poeni.xlsx
+++ b/6_semestar/Poeni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\Fakultetski_Materijal\6_semestar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46FC1905-8F4E-4823-9DB7-5836E0534A4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD045D65-0E0E-4765-B9C5-B8F506FF800D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -177,7 +177,7 @@
       <charset val="177"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -202,12 +202,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1" tint="4.9989318521683403E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -371,7 +365,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -394,16 +388,13 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -895,9 +886,9 @@
       <c r="Q15" s="6"/>
       <c r="R15" s="5"/>
       <c r="S15" s="5"/>
-      <c r="T15" s="9"/>
+      <c r="T15" s="8"/>
       <c r="U15" s="6"/>
-      <c r="V15" s="10"/>
+      <c r="V15" s="9"/>
     </row>
     <row r="16" spans="10:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J16" s="4" t="s">
@@ -912,15 +903,17 @@
       <c r="Q16" s="6"/>
       <c r="R16" s="6"/>
       <c r="S16" s="6"/>
-      <c r="T16" s="11"/>
+      <c r="T16" s="10"/>
       <c r="U16" s="6"/>
-      <c r="V16" s="10"/>
+      <c r="V16" s="9"/>
     </row>
     <row r="17" spans="10:22" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="J17" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="K17" s="5"/>
+      <c r="K17" s="10">
+        <v>10</v>
+      </c>
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
       <c r="N17" s="5"/>
@@ -936,93 +929,93 @@
       <c r="V17" s="7"/>
     </row>
     <row r="18" spans="10:22" ht="35.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="J18" s="12" t="s">
+      <c r="J18" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="K18" s="13">
+      <c r="K18" s="12">
         <f>SUM(K9:K17)</f>
-        <v>50</v>
-      </c>
-      <c r="L18" s="13">
+        <v>60</v>
+      </c>
+      <c r="L18" s="12">
         <f t="shared" ref="L18:V18" si="0">SUM(L9:L17)</f>
         <v>29</v>
       </c>
-      <c r="M18" s="13">
+      <c r="M18" s="12">
         <f t="shared" si="0"/>
         <v>55.5</v>
       </c>
-      <c r="N18" s="13">
+      <c r="N18" s="12">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="O18" s="13">
+      <c r="O18" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P18" s="13">
+      <c r="P18" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q18" s="13">
+      <c r="Q18" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R18" s="13">
+      <c r="R18" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S18" s="13">
+      <c r="S18" s="12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="T18" s="13">
+      <c r="T18" s="12">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="U18" s="13">
+      <c r="U18" s="12">
         <f t="shared" si="0"/>
         <v>17.75</v>
       </c>
-      <c r="V18" s="14">
+      <c r="V18" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="10:22" x14ac:dyDescent="0.25">
-      <c r="K19" s="15">
+      <c r="K19" s="14">
         <v>10</v>
       </c>
-      <c r="L19" s="15">
+      <c r="L19" s="14">
         <v>9</v>
       </c>
-      <c r="M19" s="15">
+      <c r="M19" s="14">
         <v>9</v>
       </c>
-      <c r="N19" s="15" t="s">
+      <c r="N19" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="O19" s="15" t="s">
+      <c r="O19" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="P19" s="15">
+      <c r="P19" s="14">
         <v>10</v>
       </c>
-      <c r="Q19" s="15">
+      <c r="Q19" s="14">
         <v>9</v>
       </c>
-      <c r="R19" s="15">
+      <c r="R19" s="14">
         <v>9</v>
       </c>
-      <c r="S19" s="15">
+      <c r="S19" s="14">
         <v>10</v>
       </c>
-      <c r="T19" s="15">
+      <c r="T19" s="14">
         <v>10</v>
       </c>
-      <c r="U19" s="15">
+      <c r="U19" s="14">
         <v>10</v>
       </c>
-      <c r="V19" s="15">
+      <c r="V19" s="14">
         <v>10</v>
       </c>
     </row>

--- a/6_semestar/Poeni.xlsx
+++ b/6_semestar/Poeni.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\Fakultetski_Materijal\6_semestar\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\gitHub\Fakultetski_Materijal\6_semestar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD045D65-0E0E-4765-B9C5-B8F506FF800D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E514253-3493-4782-908F-DD3D4999A2DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>PREDMET</t>
   </si>
@@ -107,14 +107,17 @@
     <t>UKUPNO</t>
   </si>
   <si>
-    <t>?</t>
+    <t>POLAGAO</t>
+  </si>
+  <si>
+    <t>TEK TREBA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -176,8 +179,16 @@
       <name val="Aharoni"/>
       <charset val="177"/>
     </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="2"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -213,7 +224,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -365,7 +394,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -382,31 +411,45 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -692,29 +735,41 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="J8:V19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="J4:V19"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="10" max="10" width="20.140625" customWidth="1"/>
+    <col min="10" max="10" width="20.109375" customWidth="1"/>
     <col min="11" max="11" width="9" customWidth="1"/>
-    <col min="12" max="12" width="9.28515625" customWidth="1"/>
-    <col min="13" max="13" width="12.140625" customWidth="1"/>
-    <col min="14" max="14" width="11.28515625" customWidth="1"/>
-    <col min="15" max="15" width="12.28515625" customWidth="1"/>
+    <col min="12" max="12" width="9.33203125" customWidth="1"/>
+    <col min="13" max="13" width="12.109375" customWidth="1"/>
+    <col min="14" max="14" width="11.33203125" customWidth="1"/>
+    <col min="15" max="15" width="12.33203125" customWidth="1"/>
     <col min="16" max="16" width="13" customWidth="1"/>
-    <col min="17" max="17" width="8.42578125" customWidth="1"/>
-    <col min="18" max="18" width="7.85546875" customWidth="1"/>
-    <col min="19" max="19" width="12.7109375" customWidth="1"/>
+    <col min="17" max="17" width="10.88671875" customWidth="1"/>
+    <col min="18" max="18" width="7.88671875" customWidth="1"/>
+    <col min="19" max="19" width="12.6640625" customWidth="1"/>
     <col min="20" max="20" width="9" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" customWidth="1"/>
+    <col min="21" max="21" width="10.5546875" customWidth="1"/>
     <col min="22" max="22" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="8" spans="10:22" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="10:22" x14ac:dyDescent="0.3">
+      <c r="N4" s="13"/>
+      <c r="O4" s="11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="10:22" x14ac:dyDescent="0.3">
+      <c r="N5" s="17"/>
+      <c r="O5" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="10:22" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="J8" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="K8" s="19" t="s">
         <v>1</v>
       </c>
       <c r="L8" s="2" t="s">
@@ -741,51 +796,55 @@
       <c r="S8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="T8" s="2" t="s">
+      <c r="T8" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="U8" s="2" t="s">
+      <c r="U8" s="19" t="s">
         <v>11</v>
       </c>
       <c r="V8" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="10:22" ht="33" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="10:22" ht="33" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="J9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="K9" s="5"/>
+      <c r="K9" s="20"/>
       <c r="L9" s="5"/>
-      <c r="M9" s="6">
+      <c r="M9" s="14">
         <v>20</v>
       </c>
       <c r="N9" s="5"/>
-      <c r="O9" s="6"/>
+      <c r="O9" s="14">
+        <v>50</v>
+      </c>
       <c r="P9" s="5"/>
-      <c r="Q9" s="6"/>
+      <c r="Q9" s="14">
+        <v>18.399999999999999</v>
+      </c>
       <c r="R9" s="5"/>
       <c r="S9" s="5"/>
-      <c r="T9" s="6">
+      <c r="T9" s="14">
         <v>20</v>
       </c>
-      <c r="U9" s="6">
+      <c r="U9" s="14">
         <v>17.75</v>
       </c>
-      <c r="V9" s="7"/>
-    </row>
-    <row r="10" spans="10:22" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V9" s="6"/>
+    </row>
+    <row r="10" spans="10:22" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="J10" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="K10" s="5"/>
-      <c r="L10" s="6">
+      <c r="K10" s="20"/>
+      <c r="L10" s="14">
         <v>20</v>
       </c>
-      <c r="M10" s="6">
+      <c r="M10" s="14">
         <v>20</v>
       </c>
-      <c r="N10" s="6">
+      <c r="N10" s="14">
         <v>30</v>
       </c>
       <c r="O10" s="5"/>
@@ -793,19 +852,19 @@
       <c r="Q10" s="5"/>
       <c r="R10" s="5"/>
       <c r="S10" s="5"/>
-      <c r="T10" s="5"/>
-      <c r="U10" s="8"/>
-      <c r="V10" s="7"/>
-    </row>
-    <row r="11" spans="10:22" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T10" s="20"/>
+      <c r="U10" s="20"/>
+      <c r="V10" s="6"/>
+    </row>
+    <row r="11" spans="10:22" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="J11" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="K11" s="5"/>
-      <c r="L11" s="6">
+      <c r="K11" s="20"/>
+      <c r="L11" s="14">
         <v>4.5</v>
       </c>
-      <c r="M11" s="6">
+      <c r="M11" s="14">
         <v>15.5</v>
       </c>
       <c r="N11" s="5"/>
@@ -814,51 +873,53 @@
       <c r="Q11" s="5"/>
       <c r="R11" s="5"/>
       <c r="S11" s="5"/>
-      <c r="T11" s="5"/>
-      <c r="U11" s="8"/>
-      <c r="V11" s="7"/>
-    </row>
-    <row r="12" spans="10:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T11" s="20"/>
+      <c r="U11" s="20"/>
+      <c r="V11" s="6"/>
+    </row>
+    <row r="12" spans="10:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="J12" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="K12" s="5"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="6"/>
+      <c r="K12" s="20"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="14">
+        <v>30</v>
+      </c>
       <c r="O12" s="5"/>
       <c r="P12" s="5"/>
       <c r="Q12" s="5"/>
       <c r="R12" s="5"/>
       <c r="S12" s="5"/>
-      <c r="T12" s="5"/>
-      <c r="U12" s="8"/>
-      <c r="V12" s="7"/>
-    </row>
-    <row r="13" spans="10:22" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T12" s="20"/>
+      <c r="U12" s="20"/>
+      <c r="V12" s="6"/>
+    </row>
+    <row r="13" spans="10:22" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="J13" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="K13" s="5"/>
-      <c r="L13" s="6">
+      <c r="K13" s="20"/>
+      <c r="L13" s="14">
         <v>4.5</v>
       </c>
-      <c r="M13" s="6"/>
+      <c r="M13" s="15"/>
       <c r="N13" s="5"/>
       <c r="O13" s="5"/>
       <c r="P13" s="5"/>
       <c r="Q13" s="5"/>
       <c r="R13" s="5"/>
       <c r="S13" s="5"/>
-      <c r="T13" s="5"/>
-      <c r="U13" s="8"/>
-      <c r="V13" s="7"/>
-    </row>
-    <row r="14" spans="10:22" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T13" s="20"/>
+      <c r="U13" s="20"/>
+      <c r="V13" s="6"/>
+    </row>
+    <row r="14" spans="10:22" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="J14" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="K14" s="6">
+      <c r="K14" s="14">
         <v>50</v>
       </c>
       <c r="L14" s="5"/>
@@ -867,51 +928,61 @@
       <c r="O14" s="5"/>
       <c r="P14" s="5"/>
       <c r="Q14" s="5"/>
-      <c r="R14" s="6"/>
-      <c r="S14" s="6"/>
-      <c r="T14" s="5"/>
-      <c r="U14" s="8"/>
-      <c r="V14" s="7"/>
-    </row>
-    <row r="15" spans="10:22" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R14" s="15"/>
+      <c r="S14" s="15"/>
+      <c r="T14" s="20"/>
+      <c r="U14" s="20"/>
+      <c r="V14" s="6"/>
+    </row>
+    <row r="15" spans="10:22" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="J15" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="K15" s="5"/>
+      <c r="K15" s="20"/>
       <c r="L15" s="5"/>
       <c r="M15" s="5"/>
       <c r="N15" s="5"/>
-      <c r="O15" s="6"/>
-      <c r="P15" s="6"/>
-      <c r="Q15" s="6"/>
+      <c r="O15" s="15"/>
+      <c r="P15" s="14"/>
+      <c r="Q15" s="15"/>
       <c r="R15" s="5"/>
       <c r="S15" s="5"/>
-      <c r="T15" s="8"/>
-      <c r="U15" s="6"/>
-      <c r="V15" s="9"/>
-    </row>
-    <row r="16" spans="10:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T15" s="20"/>
+      <c r="U15" s="14">
+        <v>40</v>
+      </c>
+      <c r="V15" s="12"/>
+    </row>
+    <row r="16" spans="10:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="J16" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6"/>
+      <c r="K16" s="14">
+        <v>40</v>
+      </c>
+      <c r="L16" s="14"/>
       <c r="M16" s="5"/>
-      <c r="N16" s="6"/>
+      <c r="N16" s="15"/>
       <c r="O16" s="5"/>
-      <c r="P16" s="6"/>
-      <c r="Q16" s="6"/>
-      <c r="R16" s="6"/>
-      <c r="S16" s="6"/>
-      <c r="T16" s="10"/>
-      <c r="U16" s="6"/>
-      <c r="V16" s="9"/>
-    </row>
-    <row r="17" spans="10:22" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P16" s="15"/>
+      <c r="Q16" s="15"/>
+      <c r="R16" s="14">
+        <v>50</v>
+      </c>
+      <c r="S16" s="15"/>
+      <c r="T16" s="14">
+        <v>40</v>
+      </c>
+      <c r="U16" s="14">
+        <v>40</v>
+      </c>
+      <c r="V16" s="16"/>
+    </row>
+    <row r="17" spans="10:22" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="J17" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="K17" s="10">
+      <c r="K17" s="14">
         <v>10</v>
       </c>
       <c r="L17" s="5"/>
@@ -922,102 +993,84 @@
       <c r="Q17" s="5"/>
       <c r="R17" s="5"/>
       <c r="S17" s="5"/>
-      <c r="T17" s="6">
+      <c r="T17" s="14">
         <v>40</v>
       </c>
-      <c r="U17" s="8"/>
-      <c r="V17" s="7"/>
-    </row>
-    <row r="18" spans="10:22" ht="35.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="J18" s="11" t="s">
+      <c r="U17" s="7"/>
+      <c r="V17" s="6"/>
+    </row>
+    <row r="18" spans="10:22" ht="35.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="J18" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="K18" s="12">
+      <c r="K18" s="9">
         <f>SUM(K9:K17)</f>
-        <v>60</v>
-      </c>
-      <c r="L18" s="12">
+        <v>100</v>
+      </c>
+      <c r="L18" s="9">
         <f t="shared" ref="L18:V18" si="0">SUM(L9:L17)</f>
         <v>29</v>
       </c>
-      <c r="M18" s="12">
+      <c r="M18" s="9">
         <f t="shared" si="0"/>
         <v>55.5</v>
       </c>
-      <c r="N18" s="12">
+      <c r="N18" s="9">
         <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="O18" s="12">
+        <v>60</v>
+      </c>
+      <c r="O18" s="9">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="P18" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P18" s="12">
+      <c r="Q18" s="9">
+        <f t="shared" si="0"/>
+        <v>18.399999999999999</v>
+      </c>
+      <c r="R18" s="9">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="S18" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q18" s="12">
+      <c r="T18" s="9">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="U18" s="9">
+        <f t="shared" si="0"/>
+        <v>97.75</v>
+      </c>
+      <c r="V18" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R18" s="12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S18" s="12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="T18" s="12">
-        <f t="shared" si="0"/>
-        <v>60</v>
-      </c>
-      <c r="U18" s="12">
-        <f t="shared" si="0"/>
-        <v>17.75</v>
-      </c>
-      <c r="V18" s="13">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="10:22" x14ac:dyDescent="0.25">
-      <c r="K19" s="14">
+    </row>
+    <row r="19" spans="10:22" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="K19" s="18">
         <v>10</v>
       </c>
-      <c r="L19" s="14">
-        <v>9</v>
-      </c>
-      <c r="M19" s="14">
-        <v>9</v>
-      </c>
-      <c r="N19" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="O19" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="P19" s="14">
+      <c r="L19" s="18"/>
+      <c r="M19" s="18"/>
+      <c r="N19" s="18"/>
+      <c r="O19" s="18"/>
+      <c r="P19" s="18"/>
+      <c r="Q19" s="18"/>
+      <c r="R19" s="18"/>
+      <c r="S19" s="18"/>
+      <c r="T19" s="18">
         <v>10</v>
       </c>
-      <c r="Q19" s="14">
-        <v>9</v>
-      </c>
-      <c r="R19" s="14">
-        <v>9</v>
-      </c>
-      <c r="S19" s="14">
+      <c r="U19" s="18">
         <v>10</v>
       </c>
-      <c r="T19" s="14">
-        <v>10</v>
-      </c>
-      <c r="U19" s="14">
-        <v>10</v>
-      </c>
-      <c r="V19" s="14">
-        <v>10</v>
-      </c>
+      <c r="V19" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/6_semestar/Poeni.xlsx
+++ b/6_semestar/Poeni.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\gitHub\Fakultetski_Materijal\6_semestar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E514253-3493-4782-908F-DD3D4999A2DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B0893CF-C47F-4E98-9C1C-67DB11B9AFCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
   <si>
     <t>PREDMET</t>
   </si>
@@ -111,6 +111,9 @@
   </si>
   <si>
     <t>TEK TREBA</t>
+  </si>
+  <si>
+    <t>?</t>
   </si>
 </sst>
 </file>
@@ -394,7 +397,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -402,9 +405,6 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -439,9 +439,6 @@
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -449,7 +446,7 @@
     <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -754,14 +751,14 @@
   </cols>
   <sheetData>
     <row r="4" spans="10:22" x14ac:dyDescent="0.3">
-      <c r="N4" s="13"/>
-      <c r="O4" s="11" t="s">
+      <c r="N4" s="12"/>
+      <c r="O4" s="10" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5" spans="10:22" x14ac:dyDescent="0.3">
-      <c r="N5" s="17"/>
-      <c r="O5" s="11" t="s">
+      <c r="N5" s="15"/>
+      <c r="O5" s="10" t="s">
         <v>24</v>
       </c>
     </row>
@@ -769,308 +766,336 @@
       <c r="J8" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="K8" s="19" t="s">
+      <c r="K8" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="L8" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="M8" s="2" t="s">
+      <c r="M8" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="N8" s="2" t="s">
+      <c r="N8" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="O8" s="2" t="s">
+      <c r="O8" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="P8" s="2" t="s">
+      <c r="P8" s="17" t="s">
         <v>6</v>
       </c>
       <c r="Q8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="R8" s="2" t="s">
+      <c r="R8" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="S8" s="2" t="s">
+      <c r="S8" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="T8" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="U8" s="19" t="s">
+      <c r="T8" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="U8" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="V8" s="3" t="s">
+      <c r="V8" s="18" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="9" spans="10:22" ht="33" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="J9" s="4" t="s">
+      <c r="J9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="K9" s="20"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="14">
+      <c r="K9" s="6"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="13">
         <v>20</v>
       </c>
-      <c r="N9" s="5"/>
-      <c r="O9" s="14">
+      <c r="N9" s="4"/>
+      <c r="O9" s="13">
         <v>50</v>
       </c>
-      <c r="P9" s="5"/>
-      <c r="Q9" s="14">
+      <c r="P9" s="4"/>
+      <c r="Q9" s="13">
         <v>18.399999999999999</v>
       </c>
-      <c r="R9" s="5"/>
-      <c r="S9" s="5"/>
-      <c r="T9" s="14">
+      <c r="R9" s="4"/>
+      <c r="S9" s="4"/>
+      <c r="T9" s="13">
         <v>20</v>
       </c>
-      <c r="U9" s="14">
+      <c r="U9" s="13">
         <v>17.75</v>
       </c>
-      <c r="V9" s="6"/>
+      <c r="V9" s="5"/>
     </row>
     <row r="10" spans="10:22" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="J10" s="4" t="s">
+      <c r="J10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="K10" s="20"/>
-      <c r="L10" s="14">
+      <c r="K10" s="6"/>
+      <c r="L10" s="13">
         <v>20</v>
       </c>
-      <c r="M10" s="14">
+      <c r="M10" s="13">
         <v>20</v>
       </c>
-      <c r="N10" s="14">
+      <c r="N10" s="13">
         <v>30</v>
       </c>
-      <c r="O10" s="5"/>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="5"/>
-      <c r="R10" s="5"/>
-      <c r="S10" s="5"/>
-      <c r="T10" s="20"/>
-      <c r="U10" s="20"/>
-      <c r="V10" s="6"/>
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="4"/>
+      <c r="S10" s="4"/>
+      <c r="T10" s="6"/>
+      <c r="U10" s="6"/>
+      <c r="V10" s="5"/>
     </row>
     <row r="11" spans="10:22" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="J11" s="4" t="s">
+      <c r="J11" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="K11" s="20"/>
-      <c r="L11" s="14">
+      <c r="K11" s="6"/>
+      <c r="L11" s="13">
         <v>4.5</v>
       </c>
-      <c r="M11" s="14">
+      <c r="M11" s="13">
         <v>15.5</v>
       </c>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="5"/>
-      <c r="R11" s="5"/>
-      <c r="S11" s="5"/>
-      <c r="T11" s="20"/>
-      <c r="U11" s="20"/>
-      <c r="V11" s="6"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="4"/>
+      <c r="S11" s="4"/>
+      <c r="T11" s="6"/>
+      <c r="U11" s="6"/>
+      <c r="V11" s="5"/>
     </row>
     <row r="12" spans="10:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="J12" s="4" t="s">
+      <c r="J12" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K12" s="20"/>
-      <c r="L12" s="14"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="14">
+      <c r="K12" s="6"/>
+      <c r="L12" s="13">
+        <v>18.8</v>
+      </c>
+      <c r="M12" s="13">
+        <v>20</v>
+      </c>
+      <c r="N12" s="13">
         <v>30</v>
       </c>
-      <c r="O12" s="5"/>
-      <c r="P12" s="5"/>
-      <c r="Q12" s="5"/>
-      <c r="R12" s="5"/>
-      <c r="S12" s="5"/>
-      <c r="T12" s="20"/>
-      <c r="U12" s="20"/>
-      <c r="V12" s="6"/>
+      <c r="O12" s="4"/>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="4"/>
+      <c r="S12" s="4"/>
+      <c r="T12" s="6"/>
+      <c r="U12" s="6"/>
+      <c r="V12" s="5"/>
     </row>
     <row r="13" spans="10:22" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="J13" s="4" t="s">
+      <c r="J13" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K13" s="20"/>
-      <c r="L13" s="14">
+      <c r="K13" s="6"/>
+      <c r="L13" s="13">
         <v>4.5</v>
       </c>
-      <c r="M13" s="15"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="5"/>
-      <c r="R13" s="5"/>
-      <c r="S13" s="5"/>
-      <c r="T13" s="20"/>
-      <c r="U13" s="20"/>
-      <c r="V13" s="6"/>
+      <c r="M13" s="13">
+        <v>20</v>
+      </c>
+      <c r="N13" s="4"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="4"/>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="4"/>
+      <c r="S13" s="4"/>
+      <c r="T13" s="6"/>
+      <c r="U13" s="6"/>
+      <c r="V13" s="5"/>
     </row>
     <row r="14" spans="10:22" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="J14" s="4" t="s">
+      <c r="J14" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="K14" s="14">
+      <c r="K14" s="13">
         <v>50</v>
       </c>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="5"/>
-      <c r="R14" s="15"/>
-      <c r="S14" s="15"/>
-      <c r="T14" s="20"/>
-      <c r="U14" s="20"/>
-      <c r="V14" s="6"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="4"/>
+      <c r="P14" s="4"/>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="13"/>
+      <c r="S14" s="13">
+        <v>100</v>
+      </c>
+      <c r="T14" s="6"/>
+      <c r="U14" s="6"/>
+      <c r="V14" s="5"/>
     </row>
     <row r="15" spans="10:22" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="J15" s="4" t="s">
+      <c r="J15" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K15" s="20"/>
-      <c r="L15" s="5"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="15"/>
-      <c r="P15" s="14"/>
-      <c r="Q15" s="15"/>
-      <c r="R15" s="5"/>
-      <c r="S15" s="5"/>
-      <c r="T15" s="20"/>
-      <c r="U15" s="14">
+      <c r="K15" s="6"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="4"/>
+      <c r="N15" s="4"/>
+      <c r="O15" s="13">
+        <v>45</v>
+      </c>
+      <c r="P15" s="13"/>
+      <c r="Q15" s="14"/>
+      <c r="R15" s="4"/>
+      <c r="S15" s="4"/>
+      <c r="T15" s="6"/>
+      <c r="U15" s="13">
         <v>40</v>
       </c>
-      <c r="V15" s="12"/>
+      <c r="V15" s="11"/>
     </row>
     <row r="16" spans="10:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="J16" s="4" t="s">
+      <c r="J16" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="K16" s="14">
+      <c r="K16" s="13">
         <v>40</v>
       </c>
-      <c r="L16" s="14"/>
-      <c r="M16" s="5"/>
-      <c r="N16" s="15"/>
-      <c r="O16" s="5"/>
-      <c r="P16" s="15"/>
-      <c r="Q16" s="15"/>
-      <c r="R16" s="14">
+      <c r="L16" s="13">
         <v>50</v>
       </c>
-      <c r="S16" s="15"/>
-      <c r="T16" s="14">
+      <c r="M16" s="4"/>
+      <c r="N16" s="13">
         <v>40</v>
       </c>
-      <c r="U16" s="14">
+      <c r="O16" s="4"/>
+      <c r="P16" s="13"/>
+      <c r="Q16" s="14"/>
+      <c r="R16" s="13">
+        <v>50</v>
+      </c>
+      <c r="S16" s="6"/>
+      <c r="T16" s="13">
         <v>40</v>
       </c>
-      <c r="V16" s="16"/>
+      <c r="U16" s="13">
+        <v>40</v>
+      </c>
+      <c r="V16" s="11"/>
     </row>
     <row r="17" spans="10:22" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="J17" s="4" t="s">
+      <c r="J17" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="K17" s="14">
-        <v>10</v>
-      </c>
-      <c r="L17" s="5"/>
-      <c r="M17" s="5"/>
-      <c r="N17" s="5"/>
-      <c r="O17" s="5"/>
-      <c r="P17" s="5"/>
-      <c r="Q17" s="5"/>
-      <c r="R17" s="5"/>
-      <c r="S17" s="5"/>
-      <c r="T17" s="14">
+      <c r="K17" s="13">
+        <v>10</v>
+      </c>
+      <c r="L17" s="4"/>
+      <c r="M17" s="4"/>
+      <c r="N17" s="4"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="4"/>
+      <c r="Q17" s="4"/>
+      <c r="R17" s="4"/>
+      <c r="S17" s="4"/>
+      <c r="T17" s="13">
         <v>40</v>
       </c>
-      <c r="U17" s="7"/>
-      <c r="V17" s="6"/>
+      <c r="U17" s="6"/>
+      <c r="V17" s="5"/>
     </row>
     <row r="18" spans="10:22" ht="35.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="J18" s="8" t="s">
+      <c r="J18" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="K18" s="9">
+      <c r="K18" s="8">
         <f>SUM(K9:K17)</f>
         <v>100</v>
       </c>
-      <c r="L18" s="9">
-        <f t="shared" ref="L18:V18" si="0">SUM(L9:L17)</f>
-        <v>29</v>
-      </c>
-      <c r="M18" s="9">
+      <c r="L18" s="8">
+        <f t="shared" ref="L18:U18" si="0">SUM(L9:L17)</f>
+        <v>97.8</v>
+      </c>
+      <c r="M18" s="8">
         <f t="shared" si="0"/>
-        <v>55.5</v>
-      </c>
-      <c r="N18" s="9">
+        <v>95.5</v>
+      </c>
+      <c r="N18" s="8">
         <f t="shared" si="0"/>
-        <v>60</v>
-      </c>
-      <c r="O18" s="9">
+        <v>100</v>
+      </c>
+      <c r="O18" s="8">
+        <f t="shared" si="0"/>
+        <v>95</v>
+      </c>
+      <c r="P18" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q18" s="8">
+        <f t="shared" si="0"/>
+        <v>18.399999999999999</v>
+      </c>
+      <c r="R18" s="8">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="P18" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Q18" s="9">
-        <f t="shared" si="0"/>
-        <v>18.399999999999999</v>
-      </c>
-      <c r="R18" s="9">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="S18" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="T18" s="9">
+      <c r="S18" s="8">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="U18" s="9">
+      <c r="T18" s="8">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="U18" s="8">
         <f t="shared" si="0"/>
         <v>97.75</v>
       </c>
-      <c r="V18" s="10">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="V18" s="9" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="10:22" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="K19" s="18">
-        <v>10</v>
-      </c>
-      <c r="L19" s="18"/>
-      <c r="M19" s="18"/>
-      <c r="N19" s="18"/>
-      <c r="O19" s="18"/>
-      <c r="P19" s="18"/>
-      <c r="Q19" s="18"/>
-      <c r="R19" s="18"/>
-      <c r="S19" s="18"/>
-      <c r="T19" s="18">
-        <v>10</v>
-      </c>
-      <c r="U19" s="18">
-        <v>10</v>
-      </c>
-      <c r="V19" s="18"/>
+      <c r="K19" s="16">
+        <v>10</v>
+      </c>
+      <c r="L19" s="16">
+        <v>10</v>
+      </c>
+      <c r="M19" s="16">
+        <v>10</v>
+      </c>
+      <c r="N19" s="16">
+        <v>10</v>
+      </c>
+      <c r="O19" s="16">
+        <v>10</v>
+      </c>
+      <c r="P19" s="16">
+        <v>10</v>
+      </c>
+      <c r="Q19" s="16"/>
+      <c r="R19" s="16">
+        <v>10</v>
+      </c>
+      <c r="S19" s="16">
+        <v>10</v>
+      </c>
+      <c r="T19" s="16">
+        <v>10</v>
+      </c>
+      <c r="U19" s="16">
+        <v>10</v>
+      </c>
+      <c r="V19" s="16">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/6_semestar/Poeni.xlsx
+++ b/6_semestar/Poeni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\gitHub\Fakultetski_Materijal\6_semestar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B0893CF-C47F-4E98-9C1C-67DB11B9AFCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F09ABB6-6CFB-4139-A258-C0489623E755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
   <si>
     <t>PREDMET</t>
   </si>
@@ -397,14 +397,11 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -434,9 +431,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
@@ -751,14 +745,14 @@
   </cols>
   <sheetData>
     <row r="4" spans="10:22" x14ac:dyDescent="0.3">
-      <c r="N4" s="12"/>
-      <c r="O4" s="10" t="s">
+      <c r="N4" s="11"/>
+      <c r="O4" s="9" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5" spans="10:22" x14ac:dyDescent="0.3">
-      <c r="N5" s="15"/>
-      <c r="O5" s="10" t="s">
+      <c r="N5" s="13"/>
+      <c r="O5" s="9" t="s">
         <v>24</v>
       </c>
     </row>
@@ -766,334 +760,340 @@
       <c r="J8" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="K8" s="17" t="s">
+      <c r="K8" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="L8" s="17" t="s">
+      <c r="L8" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="M8" s="17" t="s">
+      <c r="M8" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="N8" s="17" t="s">
+      <c r="N8" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="O8" s="17" t="s">
+      <c r="O8" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="P8" s="17" t="s">
+      <c r="P8" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="Q8" s="2" t="s">
+      <c r="Q8" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="R8" s="17" t="s">
+      <c r="R8" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="S8" s="17" t="s">
+      <c r="S8" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="T8" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="U8" s="17" t="s">
+      <c r="T8" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="U8" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="V8" s="18" t="s">
+      <c r="V8" s="16" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="9" spans="10:22" ht="33" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="J9" s="3" t="s">
+      <c r="J9" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="K9" s="6"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="13">
+      <c r="K9" s="5"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="12">
         <v>20</v>
       </c>
-      <c r="N9" s="4"/>
-      <c r="O9" s="13">
+      <c r="N9" s="3"/>
+      <c r="O9" s="12">
         <v>50</v>
       </c>
-      <c r="P9" s="4"/>
-      <c r="Q9" s="13">
+      <c r="P9" s="3"/>
+      <c r="Q9" s="12">
         <v>18.399999999999999</v>
       </c>
-      <c r="R9" s="4"/>
-      <c r="S9" s="4"/>
-      <c r="T9" s="13">
+      <c r="R9" s="3"/>
+      <c r="S9" s="3"/>
+      <c r="T9" s="12">
         <v>20</v>
       </c>
-      <c r="U9" s="13">
+      <c r="U9" s="12">
         <v>17.75</v>
       </c>
-      <c r="V9" s="5"/>
+      <c r="V9" s="4"/>
     </row>
     <row r="10" spans="10:22" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="J10" s="3" t="s">
+      <c r="J10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K10" s="6"/>
-      <c r="L10" s="13">
+      <c r="K10" s="5"/>
+      <c r="L10" s="12">
         <v>20</v>
       </c>
-      <c r="M10" s="13">
+      <c r="M10" s="12">
         <v>20</v>
       </c>
-      <c r="N10" s="13">
+      <c r="N10" s="12">
         <v>30</v>
       </c>
-      <c r="O10" s="4"/>
-      <c r="P10" s="4"/>
-      <c r="Q10" s="4"/>
-      <c r="R10" s="4"/>
-      <c r="S10" s="4"/>
-      <c r="T10" s="6"/>
-      <c r="U10" s="6"/>
-      <c r="V10" s="5"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="3"/>
+      <c r="S10" s="3"/>
+      <c r="T10" s="5"/>
+      <c r="U10" s="5"/>
+      <c r="V10" s="4"/>
     </row>
     <row r="11" spans="10:22" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="J11" s="3" t="s">
+      <c r="J11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="K11" s="6"/>
-      <c r="L11" s="13">
+      <c r="K11" s="5"/>
+      <c r="L11" s="12">
         <v>4.5</v>
       </c>
-      <c r="M11" s="13">
+      <c r="M11" s="12">
         <v>15.5</v>
       </c>
-      <c r="N11" s="4"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="4"/>
-      <c r="Q11" s="4"/>
-      <c r="R11" s="4"/>
-      <c r="S11" s="4"/>
-      <c r="T11" s="6"/>
-      <c r="U11" s="6"/>
-      <c r="V11" s="5"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+      <c r="T11" s="5"/>
+      <c r="U11" s="5"/>
+      <c r="V11" s="4"/>
     </row>
     <row r="12" spans="10:22" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="J12" s="3" t="s">
+      <c r="J12" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="K12" s="6"/>
-      <c r="L12" s="13">
+      <c r="K12" s="5"/>
+      <c r="L12" s="12">
         <v>18.8</v>
       </c>
-      <c r="M12" s="13">
+      <c r="M12" s="12">
         <v>20</v>
       </c>
-      <c r="N12" s="13">
+      <c r="N12" s="12">
         <v>30</v>
       </c>
-      <c r="O12" s="4"/>
-      <c r="P12" s="4"/>
-      <c r="Q12" s="4"/>
-      <c r="R12" s="4"/>
-      <c r="S12" s="4"/>
-      <c r="T12" s="6"/>
-      <c r="U12" s="6"/>
-      <c r="V12" s="5"/>
+      <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="3"/>
+      <c r="S12" s="3"/>
+      <c r="T12" s="5"/>
+      <c r="U12" s="5"/>
+      <c r="V12" s="4"/>
     </row>
     <row r="13" spans="10:22" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="J13" s="3" t="s">
+      <c r="J13" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K13" s="6"/>
-      <c r="L13" s="13">
+      <c r="K13" s="5"/>
+      <c r="L13" s="12">
         <v>4.5</v>
       </c>
-      <c r="M13" s="13">
+      <c r="M13" s="12">
         <v>20</v>
       </c>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="4"/>
-      <c r="Q13" s="4"/>
-      <c r="R13" s="4"/>
-      <c r="S13" s="4"/>
-      <c r="T13" s="6"/>
-      <c r="U13" s="6"/>
-      <c r="V13" s="5"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+      <c r="P13" s="3"/>
+      <c r="Q13" s="3"/>
+      <c r="R13" s="3"/>
+      <c r="S13" s="3"/>
+      <c r="T13" s="5"/>
+      <c r="U13" s="5"/>
+      <c r="V13" s="4"/>
     </row>
     <row r="14" spans="10:22" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="J14" s="3" t="s">
+      <c r="J14" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K14" s="13">
+      <c r="K14" s="12">
         <v>50</v>
       </c>
-      <c r="L14" s="4"/>
-      <c r="M14" s="4"/>
-      <c r="N14" s="4"/>
-      <c r="O14" s="4"/>
-      <c r="P14" s="4"/>
-      <c r="Q14" s="4"/>
-      <c r="R14" s="13"/>
-      <c r="S14" s="13">
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="3"/>
+      <c r="R14" s="12"/>
+      <c r="S14" s="12">
         <v>100</v>
       </c>
-      <c r="T14" s="6"/>
-      <c r="U14" s="6"/>
-      <c r="V14" s="5"/>
+      <c r="T14" s="5"/>
+      <c r="U14" s="5"/>
+      <c r="V14" s="4"/>
     </row>
     <row r="15" spans="10:22" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="J15" s="3" t="s">
+      <c r="J15" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K15" s="6"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
-      <c r="N15" s="4"/>
-      <c r="O15" s="13">
+      <c r="K15" s="5"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="12">
         <v>45</v>
       </c>
-      <c r="P15" s="13"/>
-      <c r="Q15" s="14"/>
-      <c r="R15" s="4"/>
-      <c r="S15" s="4"/>
-      <c r="T15" s="6"/>
-      <c r="U15" s="13">
+      <c r="P15" s="12"/>
+      <c r="Q15" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="R15" s="3"/>
+      <c r="S15" s="3"/>
+      <c r="T15" s="5"/>
+      <c r="U15" s="12">
         <v>40</v>
       </c>
-      <c r="V15" s="11"/>
+      <c r="V15" s="10"/>
     </row>
     <row r="16" spans="10:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="J16" s="3" t="s">
+      <c r="J16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="K16" s="13">
+      <c r="K16" s="12">
         <v>40</v>
       </c>
-      <c r="L16" s="13">
+      <c r="L16" s="12">
         <v>50</v>
       </c>
-      <c r="M16" s="4"/>
-      <c r="N16" s="13">
+      <c r="M16" s="3"/>
+      <c r="N16" s="12">
         <v>40</v>
       </c>
-      <c r="O16" s="4"/>
-      <c r="P16" s="13"/>
-      <c r="Q16" s="14"/>
-      <c r="R16" s="13">
+      <c r="O16" s="3"/>
+      <c r="P16" s="12"/>
+      <c r="Q16" s="12">
+        <v>63.3</v>
+      </c>
+      <c r="R16" s="12">
         <v>50</v>
       </c>
-      <c r="S16" s="6"/>
-      <c r="T16" s="13">
+      <c r="S16" s="5"/>
+      <c r="T16" s="12">
         <v>40</v>
       </c>
-      <c r="U16" s="13">
+      <c r="U16" s="12">
         <v>40</v>
       </c>
-      <c r="V16" s="11"/>
+      <c r="V16" s="10"/>
     </row>
     <row r="17" spans="10:22" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="J17" s="3" t="s">
+      <c r="J17" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="K17" s="13">
-        <v>10</v>
-      </c>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
-      <c r="N17" s="4"/>
-      <c r="O17" s="4"/>
-      <c r="P17" s="4"/>
-      <c r="Q17" s="4"/>
-      <c r="R17" s="4"/>
-      <c r="S17" s="4"/>
-      <c r="T17" s="13">
+      <c r="K17" s="12">
+        <v>10</v>
+      </c>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+      <c r="P17" s="3"/>
+      <c r="Q17" s="3"/>
+      <c r="R17" s="3"/>
+      <c r="S17" s="3"/>
+      <c r="T17" s="12">
         <v>40</v>
       </c>
-      <c r="U17" s="6"/>
-      <c r="V17" s="5"/>
+      <c r="U17" s="5"/>
+      <c r="V17" s="4"/>
     </row>
     <row r="18" spans="10:22" ht="35.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="J18" s="7" t="s">
+      <c r="J18" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K18" s="8">
+      <c r="K18" s="7">
         <f>SUM(K9:K17)</f>
         <v>100</v>
       </c>
-      <c r="L18" s="8">
+      <c r="L18" s="7">
         <f t="shared" ref="L18:U18" si="0">SUM(L9:L17)</f>
         <v>97.8</v>
       </c>
-      <c r="M18" s="8">
+      <c r="M18" s="7">
         <f t="shared" si="0"/>
         <v>95.5</v>
       </c>
-      <c r="N18" s="8">
+      <c r="N18" s="7">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="O18" s="8">
+      <c r="O18" s="7">
         <f t="shared" si="0"/>
         <v>95</v>
       </c>
-      <c r="P18" s="8" t="s">
+      <c r="P18" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="Q18" s="8">
+      <c r="Q18" s="7">
         <f t="shared" si="0"/>
-        <v>18.399999999999999</v>
-      </c>
-      <c r="R18" s="8">
+        <v>81.699999999999989</v>
+      </c>
+      <c r="R18" s="7">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="S18" s="8">
+      <c r="S18" s="7">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="T18" s="8">
+      <c r="T18" s="7">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="U18" s="8">
+      <c r="U18" s="7">
         <f t="shared" si="0"/>
         <v>97.75</v>
       </c>
-      <c r="V18" s="9" t="s">
+      <c r="V18" s="8" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="19" spans="10:22" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="K19" s="16">
-        <v>10</v>
-      </c>
-      <c r="L19" s="16">
-        <v>10</v>
-      </c>
-      <c r="M19" s="16">
-        <v>10</v>
-      </c>
-      <c r="N19" s="16">
-        <v>10</v>
-      </c>
-      <c r="O19" s="16">
-        <v>10</v>
-      </c>
-      <c r="P19" s="16">
-        <v>10</v>
-      </c>
-      <c r="Q19" s="16"/>
-      <c r="R19" s="16">
-        <v>10</v>
-      </c>
-      <c r="S19" s="16">
-        <v>10</v>
-      </c>
-      <c r="T19" s="16">
-        <v>10</v>
-      </c>
-      <c r="U19" s="16">
-        <v>10</v>
-      </c>
-      <c r="V19" s="16">
+      <c r="K19" s="14">
+        <v>10</v>
+      </c>
+      <c r="L19" s="14">
+        <v>10</v>
+      </c>
+      <c r="M19" s="14">
+        <v>10</v>
+      </c>
+      <c r="N19" s="14">
+        <v>10</v>
+      </c>
+      <c r="O19" s="14">
+        <v>10</v>
+      </c>
+      <c r="P19" s="14">
+        <v>10</v>
+      </c>
+      <c r="Q19" s="14">
+        <v>10</v>
+      </c>
+      <c r="R19" s="14">
+        <v>10</v>
+      </c>
+      <c r="S19" s="14">
+        <v>10</v>
+      </c>
+      <c r="T19" s="14">
+        <v>10</v>
+      </c>
+      <c r="U19" s="14">
+        <v>10</v>
+      </c>
+      <c r="V19" s="14">
         <v>10</v>
       </c>
     </row>
